--- a/sample_data/combined1.xlsx
+++ b/sample_data/combined1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DataCombiner\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D08157F-0D85-4061-86DB-46207B9944C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4C74A8-B035-4944-8C4F-ED2446ED2B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41190" yWindow="2580" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4635" yWindow="6390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>names</t>
   </si>
@@ -48,16 +48,13 @@
     <t>max</t>
   </si>
   <si>
-    <t>book1 attend?</t>
-  </si>
-  <si>
-    <t>testfile1 attend?</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>n</t>
+    <t>testfile1 phone</t>
+  </si>
+  <si>
+    <t>book1 phone</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -383,64 +380,64 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
+      <c r="B3">
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
+      <c r="C4">
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
+      <c r="B5">
+        <v>121</v>
+      </c>
+      <c r="C5">
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
+      <c r="C6">
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
